--- a/data/geography/india_climate_energy_dashboard/IndiaClimateEnergyDashboard_Complete.xlsx
+++ b/data/geography/india_climate_energy_dashboard/IndiaClimateEnergyDashboard_Complete.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kriehl\Documents\GitHub\mit_ai_hackathon_2025\data\geography\india_climate_energy_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20074EA2-4DFB-4942-A709-C93E7B949278}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAB312FA-DBAC-4D27-B2D1-A044C6A38CE5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="76">
   <si>
     <t>Electricity</t>
   </si>
@@ -54,9 +54,6 @@
     <t>Chhattisgarh</t>
   </si>
   <si>
-    <t>Installed Capacity</t>
-  </si>
-  <si>
     <t>MW</t>
   </si>
   <si>
@@ -195,18 +192,9 @@
     <t>West Bengal</t>
   </si>
   <si>
-    <t>GDP</t>
-  </si>
-  <si>
-    <t>SectoralGVA</t>
-  </si>
-  <si>
     <t>Population</t>
   </si>
   <si>
-    <t>IncomePerCapita</t>
-  </si>
-  <si>
     <t>ConstPrice</t>
   </si>
   <si>
@@ -241,6 +229,30 @@
   </si>
   <si>
     <t>Uttaranchal</t>
+  </si>
+  <si>
+    <t>GDP [ConstPrice]</t>
+  </si>
+  <si>
+    <t>GDP [CurrPrice]</t>
+  </si>
+  <si>
+    <t>SectoralGVA [ConstPrice]</t>
+  </si>
+  <si>
+    <t>IncomePerCapita [CurrPrice]</t>
+  </si>
+  <si>
+    <t>SectoralGVA [CurrPrice]</t>
+  </si>
+  <si>
+    <t>IncomePerCapita [ConstPrice]</t>
+  </si>
+  <si>
+    <t>Installed Capacity [loc]</t>
+  </si>
+  <si>
+    <t>Installed Capacity [dec]</t>
   </si>
 </sst>
 </file>
@@ -650,93 +662,93 @@
         <v>0</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="X1" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>9</v>
+        <v>74</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="D2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="I2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="J2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="K2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="L2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="6" t="s">
-        <v>19</v>
-      </c>
       <c r="M2" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="O2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O2" s="6" t="s">
-        <v>23</v>
-      </c>
       <c r="P2" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="S2" s="6" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="T2" s="6" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="U2" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="V2" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="W2" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="X2" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="V2" s="6" t="s">
+      <c r="Y2" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="W2" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="X2" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y2" s="6" t="s">
-        <v>63</v>
-      </c>
       <c r="Z2" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AA2" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:27" s="8" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -744,79 +756,79 @@
         <v>1</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P3" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="R3" s="8" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="S3" s="8" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="T3" s="8" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="V3" s="8" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="W3" s="8" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="X3" s="8" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="Y3" s="8" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="Z3" s="8" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="AA3" s="8" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
@@ -904,7 +916,7 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B5">
         <v>127.87</v>
@@ -1443,7 +1455,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B12">
         <v>46.47</v>
@@ -1502,7 +1514,7 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D13" s="1"/>
       <c r="J13" s="1"/>
@@ -1520,7 +1532,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D14" s="1"/>
       <c r="J14" s="1"/>
@@ -1538,7 +1550,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B15">
         <v>45509.27</v>
@@ -1613,7 +1625,7 @@
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B16">
         <v>7123.68</v>
@@ -1688,7 +1700,7 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B17">
         <v>2510.66</v>
@@ -1771,7 +1783,7 @@
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B18">
         <v>74.88</v>
@@ -1846,7 +1858,7 @@
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B19">
         <v>11330.42</v>
@@ -1921,7 +1933,7 @@
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B20">
         <v>3731.12</v>
@@ -1996,7 +2008,7 @@
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B21">
         <v>5234.1899999999996</v>
@@ -2069,7 +2081,7 @@
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B22">
         <v>30793.64</v>
@@ -2152,7 +2164,7 @@
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23">
         <v>3650.65</v>
@@ -2227,7 +2239,7 @@
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B24">
         <v>30.1</v>
@@ -2280,7 +2292,7 @@
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B25">
         <v>137.79</v>
@@ -2325,7 +2337,7 @@
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B26">
         <v>30090.080000000002</v>
@@ -2408,7 +2420,7 @@
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B27">
         <v>44267.58</v>
@@ -2491,7 +2503,7 @@
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B28">
         <v>158.72999999999999</v>
@@ -2570,7 +2582,7 @@
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B29">
         <v>372.48</v>
@@ -2651,7 +2663,7 @@
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B30">
         <v>133.47999999999999</v>
@@ -2730,7 +2742,7 @@
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B31">
         <v>110.71</v>
@@ -2809,7 +2821,7 @@
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B32">
         <v>12322.57</v>
@@ -2882,7 +2894,7 @@
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B33">
         <v>68.03</v>
@@ -2961,7 +2973,7 @@
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B34">
         <v>8641.93</v>
@@ -3036,7 +3048,7 @@
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B35">
         <v>35491.879999999997</v>
@@ -3117,7 +3129,7 @@
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B36">
         <v>2341.79</v>
@@ -3196,7 +3208,7 @@
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B37">
         <v>37452.43</v>
@@ -3279,7 +3291,7 @@
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B38">
         <v>15353.47</v>
@@ -3362,7 +3374,7 @@
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B39">
         <v>1101.21</v>
@@ -3443,7 +3455,7 @@
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B40">
         <v>5359.14</v>
@@ -3524,7 +3536,7 @@
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B41">
         <v>31510.79</v>
@@ -3607,7 +3619,7 @@
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B42">
         <v>15529.78</v>
